--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T10:06:59+00:00</t>
+    <t>2026-08-20T14:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,7 +846,7 @@
     <t>The type of relationship this person has to the patient (father, mother, brother etc.).</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-PersonalRelationshipRoleType-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-PersonalRelationshipRoleType-cisis|20260716085851</t>
   </si>
   <si>
     <t>code</t>
@@ -1118,7 +1118,7 @@
     <t>The actual condition specified. Could be a coded condition (like MI or Diabetes) or a less specific string like 'cancer' depending on how much is known about the condition and the capabilities of the creating system.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-code-probleme-cisis|20260716085853</t>
   </si>
   <si>
     <t>.value</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T14:37:13+00:00</t>
+    <t>2026-08-25T08:25:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T08:25:54+00:00</t>
+    <t>2026-08-25T13:09:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:09:33+00:00</t>
+    <t>2026-08-25T13:40:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T13:40:20+00:00</t>
+    <t>2026-08-25T14:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T14:52:49+00:00</t>
+    <t>2026-08-26T13:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:43:53+00:00</t>
+    <t>2026-08-26T14:38:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
+++ b/qaFHIRErrors/ig/StructureDefinition-fr-family-member-history-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T14:38:07+00:00</t>
+    <t>2026-08-27T07:35:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
